--- a/Ejercicios_Estadistica_Alumnos.xlsx
+++ b/Ejercicios_Estadistica_Alumnos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10303"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Proyectos/cursos_activos/inserta_once/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\curso_big_data\analisis_estadistico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54222956-CA8B-9540-87B0-F23EEB278FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8584B8-F832-483A-9EAB-1D91A572D032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="740" windowWidth="38080" windowHeight="19940" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Base" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,14 @@
     <sheet name="3_Satisfaccion" sheetId="4" r:id="rId4"/>
     <sheet name="4_Probabilidad" sheetId="5" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">'1_Precios'!$A$5:$A$46</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'1_Precios'!$B$4</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'1_Precios'!$B$5:$B$46</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'1_Precios'!$A$5:$A$46</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">'1_Precios'!$B$4</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">'1_Precios'!$B$5:$B$46</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -493,7 +501,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -537,6 +545,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -601,7 +617,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -613,6 +629,7 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -628,6 +645,680 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.0</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.2</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0"/>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="clusteredColumn" uniqueId="{55CAB87C-59CB-47C1-957E-F178B90D6A4E}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.1</cx:f>
+              <cx:v>Precio_Unitario</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:binning intervalClosed="r"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="0"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1066800</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Gráfico 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3811573-C1B2-3D7C-04E9-204CC2544626}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4244340" y="2190750"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="es-ES" sz="1100"/>
+                <a:t>Este gráfico no está disponible en su versión de Excel.
+Si edita esta forma o guarda el libro en un formato de archivo diferente, el gráfico no se podrá utilizar.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -918,9 +1609,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -964,7 +1655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -1008,7 +1699,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -1052,7 +1743,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -1096,7 +1787,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -1140,7 +1831,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -1184,7 +1875,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1006</v>
       </c>
@@ -1228,7 +1919,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1007</v>
       </c>
@@ -1272,7 +1963,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1008</v>
       </c>
@@ -1316,7 +2007,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1009</v>
       </c>
@@ -1360,7 +2051,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1010</v>
       </c>
@@ -1404,7 +2095,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1011</v>
       </c>
@@ -1448,7 +2139,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1012</v>
       </c>
@@ -1492,7 +2183,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1013</v>
       </c>
@@ -1536,7 +2227,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1014</v>
       </c>
@@ -1580,7 +2271,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1015</v>
       </c>
@@ -1624,7 +2315,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1016</v>
       </c>
@@ -1668,7 +2359,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1017</v>
       </c>
@@ -1712,7 +2403,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1018</v>
       </c>
@@ -1756,7 +2447,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1019</v>
       </c>
@@ -1800,7 +2491,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1020</v>
       </c>
@@ -1844,7 +2535,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1021</v>
       </c>
@@ -1888,7 +2579,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1022</v>
       </c>
@@ -1932,7 +2623,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1023</v>
       </c>
@@ -1976,7 +2667,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1024</v>
       </c>
@@ -2020,7 +2711,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1025</v>
       </c>
@@ -2064,7 +2755,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1026</v>
       </c>
@@ -2108,7 +2799,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1027</v>
       </c>
@@ -2152,7 +2843,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1028</v>
       </c>
@@ -2196,7 +2887,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1029</v>
       </c>
@@ -2240,7 +2931,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1030</v>
       </c>
@@ -2284,7 +2975,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1031</v>
       </c>
@@ -2328,7 +3019,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1032</v>
       </c>
@@ -2372,7 +3063,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1033</v>
       </c>
@@ -2416,7 +3107,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1034</v>
       </c>
@@ -2460,7 +3151,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1035</v>
       </c>
@@ -2504,7 +3195,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1036</v>
       </c>
@@ -2548,7 +3239,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1037</v>
       </c>
@@ -2592,7 +3283,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1038</v>
       </c>
@@ -2636,7 +3327,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1039</v>
       </c>
@@ -2680,7 +3371,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1040</v>
       </c>
@@ -2724,7 +3415,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1041</v>
       </c>
@@ -2768,7 +3459,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1042</v>
       </c>
@@ -2819,8 +3510,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M46"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
     <col min="2" max="3" width="15.6640625" customWidth="1"/>
@@ -2828,12 +3519,12 @@
     <col min="5" max="5" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -2847,7 +3538,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -2857,9 +3548,12 @@
       <c r="D5" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E5" s="4">
+        <f>AVERAGE(B5:B46)</f>
+        <v>60.011904761904759</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -2869,9 +3563,12 @@
       <c r="D6" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E6" s="4">
+        <f>MEDIAN(B5:B46)</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -2881,9 +3578,12 @@
       <c r="D7" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E7" s="4">
+        <f>_xlfn.MODE.SNGL(B5:B46)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -2893,9 +3593,12 @@
       <c r="D8" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E8" s="4">
+        <f>_xlfn.STDEV.S(B5:B46)</f>
+        <v>63.23692269082472</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -2903,7 +3606,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -2911,7 +3614,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -2922,15 +3625,16 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
       <c r="B12">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="M12" s="9"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -2938,7 +3642,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -2946,7 +3650,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -2954,7 +3658,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -2962,7 +3666,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -2970,7 +3674,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -2978,7 +3682,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -2986,7 +3690,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>71</v>
       </c>
@@ -2994,7 +3698,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -3002,7 +3706,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -3010,7 +3714,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -3018,7 +3722,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -3026,7 +3730,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>76</v>
       </c>
@@ -3034,7 +3738,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>77</v>
       </c>
@@ -3042,7 +3746,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -3050,7 +3754,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -3058,7 +3762,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -3066,7 +3770,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>81</v>
       </c>
@@ -3074,7 +3778,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -3082,7 +3786,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>83</v>
       </c>
@@ -3090,7 +3794,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>84</v>
       </c>
@@ -3098,7 +3802,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>85</v>
       </c>
@@ -3106,7 +3810,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>86</v>
       </c>
@@ -3114,7 +3818,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>87</v>
       </c>
@@ -3122,7 +3826,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -3130,7 +3834,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>89</v>
       </c>
@@ -3138,7 +3842,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>90</v>
       </c>
@@ -3146,7 +3850,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>91</v>
       </c>
@@ -3154,7 +3858,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -3162,7 +3866,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -3170,7 +3874,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -3178,7 +3882,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>95</v>
       </c>
@@ -3186,7 +3890,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>95</v>
       </c>
@@ -3194,7 +3898,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>95</v>
       </c>
@@ -3204,13 +3908,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
     <col min="2" max="3" width="15.6640625" customWidth="1"/>
@@ -3218,12 +3923,12 @@
     <col min="6" max="6" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -3240,7 +3945,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -3255,7 +3960,7 @@
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -3270,7 +3975,7 @@
       </c>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -3285,7 +3990,7 @@
       </c>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -3300,7 +4005,7 @@
       </c>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -3311,7 +4016,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -3322,7 +4027,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -3336,7 +4041,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -3347,7 +4052,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -3358,7 +4063,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -3369,7 +4074,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -3380,7 +4085,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -3391,7 +4096,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -3402,7 +4107,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -3413,7 +4118,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -3424,7 +4129,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>71</v>
       </c>
@@ -3435,7 +4140,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -3446,7 +4151,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -3457,7 +4162,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -3468,7 +4173,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -3479,7 +4184,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>76</v>
       </c>
@@ -3490,7 +4195,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>77</v>
       </c>
@@ -3501,7 +4206,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -3512,7 +4217,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -3523,7 +4228,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -3534,7 +4239,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>81</v>
       </c>
@@ -3545,7 +4250,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -3556,7 +4261,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>83</v>
       </c>
@@ -3567,7 +4272,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>84</v>
       </c>
@@ -3578,7 +4283,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>85</v>
       </c>
@@ -3589,7 +4294,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>86</v>
       </c>
@@ -3600,7 +4305,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>87</v>
       </c>
@@ -3611,7 +4316,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -3622,7 +4327,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>89</v>
       </c>
@@ -3633,7 +4338,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>90</v>
       </c>
@@ -3644,7 +4349,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>91</v>
       </c>
@@ -3655,7 +4360,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -3666,7 +4371,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -3677,7 +4382,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -3688,7 +4393,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>95</v>
       </c>
@@ -3699,7 +4404,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>95</v>
       </c>
@@ -3710,7 +4415,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>95</v>
       </c>
@@ -3729,7 +4434,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
     <col min="2" max="3" width="15.6640625" customWidth="1"/>
@@ -3737,12 +4442,12 @@
     <col min="5" max="5" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -3756,7 +4461,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -3768,7 +4473,7 @@
       </c>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -3780,7 +4485,7 @@
       </c>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -3792,7 +4497,7 @@
       </c>
       <c r="E7" s="4"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -3800,7 +4505,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -3808,7 +4513,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -3819,7 +4524,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -3833,7 +4538,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -3845,7 +4550,7 @@
       </c>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -3857,7 +4562,7 @@
       </c>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -3869,7 +4574,7 @@
       </c>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -3881,7 +4586,7 @@
       </c>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -3893,7 +4598,7 @@
       </c>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -3901,7 +4606,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -3909,7 +4614,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -3920,7 +4625,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>71</v>
       </c>
@@ -3928,7 +4633,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -3936,7 +4641,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -3944,7 +4649,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -3952,7 +4657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -3960,7 +4665,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>76</v>
       </c>
@@ -3968,7 +4673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>77</v>
       </c>
@@ -3976,7 +4681,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -3984,7 +4689,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -3992,7 +4697,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -4000,7 +4705,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>81</v>
       </c>
@@ -4008,7 +4713,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -4016,7 +4721,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>83</v>
       </c>
@@ -4024,7 +4729,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>84</v>
       </c>
@@ -4032,7 +4737,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>85</v>
       </c>
@@ -4040,7 +4745,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>86</v>
       </c>
@@ -4048,7 +4753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>87</v>
       </c>
@@ -4056,7 +4761,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -4064,7 +4769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>89</v>
       </c>
@@ -4072,7 +4777,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>90</v>
       </c>
@@ -4080,7 +4785,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>91</v>
       </c>
@@ -4088,7 +4793,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -4096,7 +4801,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -4104,7 +4809,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -4112,7 +4817,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>95</v>
       </c>
@@ -4120,7 +4825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>95</v>
       </c>
@@ -4128,7 +4833,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>95</v>
       </c>
@@ -4144,25 +4849,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98BB36B-BB56-6748-8634-193EA745B178}">
   <dimension ref="A1:G46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
     <col min="2" max="4" width="15.6640625" customWidth="1"/>
     <col min="5" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D3" s="3" t="s">
         <v>148</v>
       </c>
       <c r="E3" s="4"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -4170,7 +4875,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -4190,7 +4895,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -4204,7 +4909,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="7"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -4218,7 +4923,7 @@
       <c r="F7" s="8"/>
       <c r="G7" s="7"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -4232,7 +4937,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="7"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -4246,7 +4951,7 @@
       <c r="F9" s="8"/>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -4254,7 +4959,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -4265,7 +4970,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -4276,7 +4981,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -4287,7 +4992,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -4295,7 +5000,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -4306,7 +5011,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -4314,7 +5019,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -4325,7 +5030,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -4333,7 +5038,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -4341,7 +5046,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>71</v>
       </c>
@@ -4349,7 +5054,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -4357,7 +5062,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -4365,7 +5070,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -4373,7 +5078,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -4381,7 +5086,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>76</v>
       </c>
@@ -4389,7 +5094,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>77</v>
       </c>
@@ -4397,7 +5102,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -4405,7 +5110,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -4413,7 +5118,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -4421,7 +5126,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>81</v>
       </c>
@@ -4429,7 +5134,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -4437,7 +5142,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>83</v>
       </c>
@@ -4445,7 +5150,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>84</v>
       </c>
@@ -4453,7 +5158,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>85</v>
       </c>
@@ -4461,7 +5166,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>86</v>
       </c>
@@ -4469,7 +5174,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>87</v>
       </c>
@@ -4477,7 +5182,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>88</v>
       </c>
@@ -4485,7 +5190,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>89</v>
       </c>
@@ -4493,7 +5198,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>90</v>
       </c>
@@ -4501,7 +5206,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>91</v>
       </c>
@@ -4509,7 +5214,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -4517,7 +5222,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -4525,7 +5230,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -4533,7 +5238,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>95</v>
       </c>
@@ -4541,7 +5246,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>95</v>
       </c>
@@ -4549,7 +5254,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>95</v>
       </c>

--- a/Ejercicios_Estadistica_Alumnos.xlsx
+++ b/Ejercicios_Estadistica_Alumnos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\curso_big_data\analisis_estadistico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8584B8-F832-483A-9EAB-1D91A572D032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF6D11D-7D3A-4293-AF94-6BF240F156C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Base" sheetId="1" r:id="rId1"/>
@@ -23,9 +23,6 @@
     <definedName name="_xlchart.v1.0" hidden="1">'1_Precios'!$A$5:$A$46</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">'1_Precios'!$B$4</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">'1_Precios'!$B$5:$B$46</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'1_Precios'!$A$5:$A$46</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'1_Precios'!$B$4</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'1_Precios'!$B$5:$B$46</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -647,6 +644,548 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.3509101802207891E-2"/>
+          <c:y val="0.17389455384931729"/>
+          <c:w val="0.87151659758370359"/>
+          <c:h val="0.72476236763152735"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'2_Beneficios'!$B$5:$B$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="42"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'2_Beneficios'!$C$5:$C$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="42"/>
+                <c:pt idx="0">
+                  <c:v>15.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-EA2C-4775-A608-ADABA3FAB8FF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1409210975"/>
+        <c:axId val="1409214335"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1409210975"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1409214335"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1409214335"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1409210975"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
@@ -691,6 +1230,46 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1238,6 +1817,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -1316,6 +2411,47 @@
         </xdr:sp>
       </mc:Fallback>
     </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>587188</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>134471</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>264458</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>8966</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3C3517F-EF45-FD13-7372-AC38BC1AB767}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3914,7 +5050,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" customWidth="1"/>
@@ -3958,7 +5094,10 @@
       <c r="E5" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="F5" s="4"/>
+      <c r="F5" s="4">
+        <f>AVERAGE(C5:C46)</f>
+        <v>32.511904761904759</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -3973,7 +5112,10 @@
       <c r="E6" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="F6" s="4"/>
+      <c r="F6" s="4">
+        <f>_xlfn.STDEV.S(C5:C46)</f>
+        <v>20.550499399082351</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -3988,7 +5130,10 @@
       <c r="E7" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="F7" s="4"/>
+      <c r="F7" s="4">
+        <f>MIN(C5:C46)</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -4003,7 +5148,10 @@
       <c r="E8" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="F8" s="4"/>
+      <c r="F8" s="4">
+        <f>MAX(C5:C46)</f>
+        <v>120</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -4096,7 +5244,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -4107,7 +5255,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -4118,7 +5266,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -4129,7 +5277,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>71</v>
       </c>
@@ -4140,7 +5288,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -4151,7 +5299,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -4162,7 +5310,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -4173,7 +5321,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -4184,7 +5332,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>76</v>
       </c>
@@ -4195,7 +5343,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>77</v>
       </c>
@@ -4206,7 +5354,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -4217,7 +5365,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -4228,7 +5376,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -4239,7 +5387,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>81</v>
       </c>
@@ -4250,7 +5398,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -4260,8 +5408,9 @@
       <c r="C31">
         <v>21</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="K31" s="9"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>83</v>
       </c>
@@ -4428,6 +5577,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Ejercicios_Estadistica_Alumnos.xlsx
+++ b/Ejercicios_Estadistica_Alumnos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\curso_big_data\analisis_estadistico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF6D11D-7D3A-4293-AF94-6BF240F156C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3881030D-BE97-40BE-8E11-9BD556AB28A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Base" sheetId="1" r:id="rId1"/>
@@ -1186,6 +1186,397 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-ES"/>
+              <a:t>Distribución</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="es-ES" baseline="0"/>
+              <a:t> de Satisfacción</a:t>
+            </a:r>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'3_Satisfaccion'!$D$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Valoración (Estrellas)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'3_Satisfaccion'!$D$12:$D$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-322C-4C87-BB21-C686C83E21A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'3_Satisfaccion'!$E$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Nº de Clientes</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'3_Satisfaccion'!$E$12:$E$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-322C-4C87-BB21-C686C83E21A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1772928336"/>
+        <c:axId val="1997121360"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1772928336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1997121360"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1997121360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1772928336"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
@@ -1309,6 +1700,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
   <cs:axisTitle>
@@ -2314,6 +2745,509 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -2437,6 +3371,47 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3C3517F-EF45-FD13-7372-AC38BC1AB767}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1066799</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>155713</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>265043</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>115957</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBCE51A7-DE47-D1B6-7E11-B91F5541CD4B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5621,7 +6596,10 @@
       <c r="D5" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="4">
+        <f>AVERAGE(B5:B46)</f>
+        <v>4.2857142857142856</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -5633,7 +6611,10 @@
       <c r="D6" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E6" s="4"/>
+      <c r="E6" s="4">
+        <f>MEDIAN(B5:B46)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -5645,7 +6626,10 @@
       <c r="D7" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="4">
+        <f>_xlfn.MODE.SNGL(B5:B46)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -5698,7 +6682,10 @@
       <c r="D12" s="3">
         <v>1</v>
       </c>
-      <c r="E12" s="4"/>
+      <c r="E12" s="4">
+        <f>COUNTIF($B$5:$B$46,D12)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -5710,7 +6697,10 @@
       <c r="D13" s="3">
         <v>2</v>
       </c>
-      <c r="E13" s="4"/>
+      <c r="E13" s="4">
+        <f t="shared" ref="E13:E16" si="0">COUNTIF($B$5:$B$46,D13)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -5722,7 +6712,10 @@
       <c r="D14" s="3">
         <v>3</v>
       </c>
-      <c r="E14" s="4"/>
+      <c r="E14" s="4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -5734,7 +6727,10 @@
       <c r="D15" s="3">
         <v>4</v>
       </c>
-      <c r="E15" s="4"/>
+      <c r="E15" s="4">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -5746,7 +6742,10 @@
       <c r="D16" s="3">
         <v>5</v>
       </c>
-      <c r="E16" s="4"/>
+      <c r="E16" s="4">
+        <f>COUNTIF($B$5:$B$46,D16)</f>
+        <v>18</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -5993,6 +6992,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Ejercicios_Estadistica_Alumnos.xlsx
+++ b/Ejercicios_Estadistica_Alumnos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\curso_big_data\analisis_estadistico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3881030D-BE97-40BE-8E11-9BD556AB28A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B286B8C2-9AA9-4FDD-B2CA-A726E0307544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Base" sheetId="1" r:id="rId1"/>
@@ -1577,6 +1577,249 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'4_Probabilidad'!$E$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Frecuencia Absoluta</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>'4_Probabilidad'!$D$6:$D$8</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>App</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Web</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Tienda</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4_Probabilidad'!$E$6:$E$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-493A-4533-ADA8-B52D89AA7F7F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
@@ -1740,6 +1983,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
   <cs:axisTitle>
@@ -3235,6 +3518,525 @@
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -3412,6 +4214,47 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBCE51A7-DE47-D1B6-7E11-B91F5541CD4B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1066800</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>660400</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACA345F5-176A-CF8B-C926-D48CAED52B79}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6698,7 +7541,7 @@
         <v>2</v>
       </c>
       <c r="E13" s="4">
-        <f t="shared" ref="E13:E16" si="0">COUNTIF($B$5:$B$46,D13)</f>
+        <f t="shared" ref="E13:E15" si="0">COUNTIF($B$5:$B$46,D13)</f>
         <v>1</v>
       </c>
     </row>
@@ -7015,7 +7858,10 @@
       <c r="D3" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E3" s="4"/>
+      <c r="E3" s="4">
+        <f>E9</f>
+        <v>42</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
@@ -7055,9 +7901,18 @@
       <c r="D6" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="7"/>
+      <c r="E6" s="4">
+        <f>COUNTIF($B$5:$B$46,D6)</f>
+        <v>11</v>
+      </c>
+      <c r="F6" s="8">
+        <f>E6/$E$9</f>
+        <v>0.26190476190476192</v>
+      </c>
+      <c r="G6" s="7">
+        <f>F6</f>
+        <v>0.26190476190476192</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -7069,9 +7924,18 @@
       <c r="D7" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="7"/>
+      <c r="E7" s="4">
+        <f t="shared" ref="E7:E8" si="0">COUNTIF($B$5:$B$46,D7)</f>
+        <v>17</v>
+      </c>
+      <c r="F7" s="8">
+        <f t="shared" ref="F7:F9" si="1">E7/$E$9</f>
+        <v>0.40476190476190477</v>
+      </c>
+      <c r="G7" s="7">
+        <f>F7</f>
+        <v>0.40476190476190477</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -7083,9 +7947,18 @@
       <c r="D8" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="7"/>
+      <c r="E8" s="4">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="F8" s="8">
+        <f>E8/$E$9</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G8" s="7">
+        <f t="shared" ref="G7:G9" si="2">F8</f>
+        <v>0.33333333333333331</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -7097,9 +7970,18 @@
       <c r="D9" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="7"/>
+      <c r="E9" s="4">
+        <f>SUM(E6:E8)</f>
+        <v>42</v>
+      </c>
+      <c r="F9" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G9" s="7">
+        <f>F9</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -7414,5 +8296,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>